--- a/SubRES_TMPL/SubRES_RSD_NewTechs_Trans.xlsx
+++ b/SubRES_TMPL/SubRES_RSD_NewTechs_Trans.xlsx
@@ -529,7 +529,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3125" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2950" uniqueCount="304">
   <si>
     <t>IE</t>
   </si>
@@ -1044,27 +1044,27 @@
     <t>R-RSDCW_X0</t>
   </si>
   <si>
+    <t>R-LT_Apt_X0</t>
+  </si>
+  <si>
+    <t>R-LT_Att_X0</t>
+  </si>
+  <si>
     <t>R-LT_Det_X0</t>
   </si>
   <si>
-    <t>R-LT_Att_X0</t>
-  </si>
-  <si>
-    <t>R-LT_Apt_X0</t>
-  </si>
-  <si>
     <t>R-RSDCD_X0</t>
   </si>
   <si>
+    <t>R-PF_Apt_X0</t>
+  </si>
+  <si>
+    <t>R-PF_Att_X0</t>
+  </si>
+  <si>
     <t>R-PF_Det_X0</t>
   </si>
   <si>
-    <t>R-PF_Att_X0</t>
-  </si>
-  <si>
-    <t>R-PF_Apt_X0</t>
-  </si>
-  <si>
     <t>R-RSDDW_X0</t>
   </si>
   <si>
@@ -1308,15 +1308,15 @@
     <t>*Space Heating (dual techs)</t>
   </si>
   <si>
+    <t>R-RSDCK_ELC_X0</t>
+  </si>
+  <si>
+    <t>R-RSDCK_GAS_X0</t>
+  </si>
+  <si>
     <t>R-RSDCK_LPG_X0</t>
   </si>
   <si>
-    <t>R-RSDCK_GAS_X0</t>
-  </si>
-  <si>
-    <t>R-RSDCK_ELC_X0</t>
-  </si>
-  <si>
     <t>R-SH_Att_GAS_X0</t>
   </si>
   <si>
@@ -1459,9 +1459,6 @@
   </si>
   <si>
     <t>*0.8</t>
-  </si>
-  <si>
-    <t>year2</t>
   </si>
 </sst>
 </file>
@@ -1591,7 +1588,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="7" tint="-0.499370008707047"/>
+      <color theme="7" tint="-0.499359995126724"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1606,7 +1603,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="7" tint="-0.499370008707047"/>
+      <color theme="7" tint="-0.499359995126724"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1683,7 +1680,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.049380000680685"/>
+        <fgColor theme="0" tint="-0.0493699982762337"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1695,7 +1692,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149389997124672"/>
+        <fgColor theme="0" tint="-0.149379998445511"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2161,7 +2158,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId2"/>
-        <a:srcRect l="4530" t="8845" r="7658" b="12837"/>
+        <a:srcRect l="4528" t="8843" r="7656" b="12835"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2288,7 +2285,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId5"/>
-        <a:srcRect l="1280" t="6475" r="3923" b="6250"/>
+        <a:srcRect l="1278" t="6474" r="3921" b="6250"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2331,7 +2328,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId6"/>
-        <a:srcRect l="3910" t="26110" r="3910" b="26109"/>
+        <a:srcRect l="3909" t="26109" r="3909" b="26107"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5739,9 +5736,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -5783,9 +5777,6 @@
       <c r="M2">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N2" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="3" spans="1:14" ht="12.75">
       <c r="A3" t="s">
@@ -5827,9 +5818,6 @@
       <c r="M3">
         <v>0.59018803418803401</v>
       </c>
-      <c r="N3" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="4" spans="1:14" ht="12.75">
       <c r="A4" t="s">
@@ -5871,9 +5859,6 @@
       <c r="M4">
         <v>1</v>
       </c>
-      <c r="N4" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="5" spans="1:14" ht="12.75">
       <c r="A5" t="s">
@@ -5915,9 +5900,6 @@
       <c r="M5">
         <v>3.07019607843137</v>
       </c>
-      <c r="N5" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="6" spans="1:14" ht="12.75">
       <c r="A6" t="s">
@@ -5959,9 +5941,6 @@
       <c r="M6">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N6" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="7" spans="1:14" ht="12.75">
       <c r="A7" t="s">
@@ -6003,9 +5982,6 @@
       <c r="M7">
         <v>0.810268817204301</v>
       </c>
-      <c r="N7" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="8" spans="1:14" ht="12.75">
       <c r="A8" t="s">
@@ -6047,9 +6023,6 @@
       <c r="M8">
         <v>0.39838442187649997</v>
       </c>
-      <c r="N8" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="9" spans="1:14" ht="12.75">
       <c r="A9" t="s">
@@ -6091,9 +6064,6 @@
       <c r="M9">
         <v>0.81016216216216197</v>
       </c>
-      <c r="N9" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="10" spans="1:14" ht="12.75">
       <c r="A10" t="s">
@@ -6135,9 +6105,6 @@
       <c r="M10">
         <v>0.80677902621722797</v>
       </c>
-      <c r="N10" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="11" spans="1:14" ht="12.75">
       <c r="A11" t="s">
@@ -6179,9 +6146,6 @@
       <c r="M11">
         <v>0.52500000000000002</v>
       </c>
-      <c r="N11" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="12" spans="1:14" ht="12.75">
       <c r="A12" t="s">
@@ -6223,9 +6187,6 @@
       <c r="M12">
         <v>0.58177777777777795</v>
       </c>
-      <c r="N12" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="13" spans="1:14" ht="12.75">
       <c r="A13" t="s">
@@ -6267,9 +6228,6 @@
       <c r="M13">
         <v>0.68804511278195502</v>
       </c>
-      <c r="N13" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="14" spans="1:14" ht="12.75">
       <c r="A14" t="s">
@@ -6311,9 +6269,6 @@
       <c r="M14">
         <v>1</v>
       </c>
-      <c r="N14" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="15" spans="1:14" ht="12.75">
       <c r="A15" t="s">
@@ -6355,9 +6310,6 @@
       <c r="M15">
         <v>0.55798087905732696</v>
       </c>
-      <c r="N15" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="16" spans="1:14" ht="12.75">
       <c r="A16" t="s">
@@ -6399,9 +6351,6 @@
       <c r="M16">
         <v>1</v>
       </c>
-      <c r="N16" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="17" spans="1:14" ht="12.75">
       <c r="A17" t="s">
@@ -6443,9 +6392,6 @@
       <c r="M17">
         <v>3.1157627118644098</v>
       </c>
-      <c r="N17" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="18" spans="1:14" ht="12.75">
       <c r="A18" t="s">
@@ -6487,9 +6433,6 @@
       <c r="M18">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N18" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="19" spans="1:14" ht="12.75">
       <c r="A19" t="s">
@@ -6531,9 +6474,6 @@
       <c r="M19">
         <v>0.81729411764705895</v>
       </c>
-      <c r="N19" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="20" spans="1:14" ht="12.75">
       <c r="A20" t="s">
@@ -6575,9 +6515,6 @@
       <c r="M20">
         <v>0.60949973059968399</v>
       </c>
-      <c r="N20" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="21" spans="1:14" ht="12.75">
       <c r="A21" t="s">
@@ -6619,9 +6556,6 @@
       <c r="M21">
         <v>0.81941558441558404</v>
       </c>
-      <c r="N21" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="22" spans="1:14" ht="12.75">
       <c r="A22" t="s">
@@ -6663,9 +6597,6 @@
       <c r="M22">
         <v>0.80707577433628297</v>
       </c>
-      <c r="N22" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="23" spans="1:14" ht="12.75">
       <c r="A23" t="s">
@@ -6707,9 +6638,6 @@
       <c r="M23">
         <v>0.55092948717948698</v>
       </c>
-      <c r="N23" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="24" spans="1:14" ht="12.75">
       <c r="A24" t="s">
@@ -6751,9 +6679,6 @@
       <c r="M24">
         <v>0.57113772455089795</v>
       </c>
-      <c r="N24" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="25" spans="1:14" ht="12.75">
       <c r="A25" t="s">
@@ -6795,9 +6720,6 @@
       <c r="M25">
         <v>0.70400656814449902</v>
       </c>
-      <c r="N25" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="26" spans="1:14" ht="12.75">
       <c r="A26" t="s">
@@ -6839,9 +6761,6 @@
       <c r="M26">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N26" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="27" spans="1:14" ht="12.75">
       <c r="A27" t="s">
@@ -6883,9 +6802,6 @@
       <c r="M27">
         <v>0.619863294600137</v>
       </c>
-      <c r="N27" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="28" spans="1:14" ht="12.75">
       <c r="A28" t="s">
@@ -6927,9 +6843,6 @@
       <c r="M28">
         <v>0.99952095808383201</v>
       </c>
-      <c r="N28" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="29" spans="1:14" ht="12.75">
       <c r="A29" t="s">
@@ -6971,9 +6884,6 @@
       <c r="M29">
         <v>3.0897837837837798</v>
       </c>
-      <c r="N29" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="30" spans="1:14" ht="12.75">
       <c r="A30" t="s">
@@ -7015,9 +6925,6 @@
       <c r="M30">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N30" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="31" spans="1:14" ht="12.75">
       <c r="A31" t="s">
@@ -7059,9 +6966,6 @@
       <c r="M31">
         <v>0.82728758169934602</v>
       </c>
-      <c r="N31" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="32" spans="1:14" ht="12.75">
       <c r="A32" t="s">
@@ -7103,9 +7007,6 @@
       <c r="M32">
         <v>0.65865731206453004</v>
       </c>
-      <c r="N32" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="33" spans="1:14" ht="12.75">
       <c r="A33" t="s">
@@ -7147,9 +7048,6 @@
       <c r="M33">
         <v>0.82280373831775699</v>
       </c>
-      <c r="N33" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="34" spans="1:14" ht="12.75">
       <c r="A34" t="s">
@@ -7191,9 +7089,6 @@
       <c r="M34">
         <v>0.82661774762699303</v>
       </c>
-      <c r="N34" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="35" spans="1:14" ht="12.75">
       <c r="A35" t="s">
@@ -7235,9 +7130,6 @@
       <c r="M35">
         <v>0.54578947368421105</v>
       </c>
-      <c r="N35" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="36" spans="1:14" ht="12.75">
       <c r="A36" t="s">
@@ -7279,9 +7171,6 @@
       <c r="M36">
         <v>0.61474226804123699</v>
       </c>
-      <c r="N36" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="37" spans="1:14" ht="12.75">
       <c r="A37" t="s">
@@ -7323,9 +7212,6 @@
       <c r="M37">
         <v>0.72928609692169399</v>
       </c>
-      <c r="N37" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="38" spans="1:14" ht="12.75">
       <c r="A38" t="s">
@@ -7367,9 +7253,6 @@
       <c r="M38">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N38" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="39" spans="1:14" ht="12.75">
       <c r="A39" t="s">
@@ -7411,9 +7294,6 @@
       <c r="M39">
         <v>0.59018803418803401</v>
       </c>
-      <c r="N39" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="40" spans="1:14" ht="12.75">
       <c r="A40" t="s">
@@ -7455,9 +7335,6 @@
       <c r="M40">
         <v>1</v>
       </c>
-      <c r="N40" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="41" spans="1:14" ht="12.75">
       <c r="A41" t="s">
@@ -7499,9 +7376,6 @@
       <c r="M41">
         <v>3.07019607843137</v>
       </c>
-      <c r="N41" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="42" spans="1:14" ht="12.75">
       <c r="A42" t="s">
@@ -7543,9 +7417,6 @@
       <c r="M42">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N42" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="43" spans="1:14" ht="12.75">
       <c r="A43" t="s">
@@ -7587,9 +7458,6 @@
       <c r="M43">
         <v>0.810268817204301</v>
       </c>
-      <c r="N43" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="44" spans="1:14" ht="12.75">
       <c r="A44" t="s">
@@ -7631,9 +7499,6 @@
       <c r="M44">
         <v>0.39838442187649997</v>
       </c>
-      <c r="N44" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="45" spans="1:14" ht="12.75">
       <c r="A45" t="s">
@@ -7675,9 +7540,6 @@
       <c r="M45">
         <v>0.81016216216216197</v>
       </c>
-      <c r="N45" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="46" spans="1:14" ht="12.75">
       <c r="A46" t="s">
@@ -7719,9 +7581,6 @@
       <c r="M46">
         <v>0.80677902621722797</v>
       </c>
-      <c r="N46" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="47" spans="1:14" ht="12.75">
       <c r="A47" t="s">
@@ -7763,9 +7622,6 @@
       <c r="M47">
         <v>0.52500000000000002</v>
       </c>
-      <c r="N47" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="48" spans="1:14" ht="12.75">
       <c r="A48" t="s">
@@ -7807,9 +7663,6 @@
       <c r="M48">
         <v>0.58177777777777795</v>
       </c>
-      <c r="N48" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="49" spans="1:14" ht="12.75">
       <c r="A49" t="s">
@@ -7851,9 +7704,6 @@
       <c r="M49">
         <v>1</v>
       </c>
-      <c r="N49" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="50" spans="1:14" ht="12.75">
       <c r="A50" t="s">
@@ -7895,9 +7745,6 @@
       <c r="M50">
         <v>0.68804511278195502</v>
       </c>
-      <c r="N50" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="51" spans="1:14" ht="12.75">
       <c r="A51" t="s">
@@ -7939,9 +7786,6 @@
       <c r="M51">
         <v>1</v>
       </c>
-      <c r="N51" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="52" spans="1:14" ht="12.75">
       <c r="A52" t="s">
@@ -7983,9 +7827,6 @@
       <c r="M52">
         <v>0.55798087905732696</v>
       </c>
-      <c r="N52" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="53" spans="1:14" ht="12.75">
       <c r="A53" t="s">
@@ -8027,9 +7868,6 @@
       <c r="M53">
         <v>1</v>
       </c>
-      <c r="N53" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="54" spans="1:14" ht="12.75">
       <c r="A54" t="s">
@@ -8071,9 +7909,6 @@
       <c r="M54">
         <v>3.1157627118644098</v>
       </c>
-      <c r="N54" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="55" spans="1:14" ht="12.75">
       <c r="A55" t="s">
@@ -8115,9 +7950,6 @@
       <c r="M55">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N55" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="56" spans="1:14" ht="12.75">
       <c r="A56" t="s">
@@ -8159,9 +7991,6 @@
       <c r="M56">
         <v>0.81729411764705895</v>
       </c>
-      <c r="N56" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="57" spans="1:14" ht="12.75">
       <c r="A57" t="s">
@@ -8203,9 +8032,6 @@
       <c r="M57">
         <v>0.60949973059968399</v>
       </c>
-      <c r="N57" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="58" spans="1:14" ht="12.75">
       <c r="A58" t="s">
@@ -8247,9 +8073,6 @@
       <c r="M58">
         <v>0.81941558441558404</v>
       </c>
-      <c r="N58" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="59" spans="1:14" ht="12.75">
       <c r="A59" t="s">
@@ -8291,9 +8114,6 @@
       <c r="M59">
         <v>0.80707577433628297</v>
       </c>
-      <c r="N59" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="60" spans="1:14" ht="12.75">
       <c r="A60" t="s">
@@ -8335,9 +8155,6 @@
       <c r="M60">
         <v>0.55092948717948698</v>
       </c>
-      <c r="N60" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="61" spans="1:14" ht="12.75">
       <c r="A61" t="s">
@@ -8379,9 +8196,6 @@
       <c r="M61">
         <v>0.57113772455089795</v>
       </c>
-      <c r="N61" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="62" spans="1:14" ht="12.75">
       <c r="A62" t="s">
@@ -8423,9 +8237,6 @@
       <c r="M62">
         <v>1</v>
       </c>
-      <c r="N62" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="63" spans="1:14" ht="12.75">
       <c r="A63" t="s">
@@ -8467,9 +8278,6 @@
       <c r="M63">
         <v>0.70400656814449902</v>
       </c>
-      <c r="N63" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="64" spans="1:14" ht="12.75">
       <c r="A64" t="s">
@@ -8511,9 +8319,6 @@
       <c r="M64">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N64" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="65" spans="1:14" ht="12.75">
       <c r="A65" t="s">
@@ -8555,9 +8360,6 @@
       <c r="M65">
         <v>0.619863294600137</v>
       </c>
-      <c r="N65" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="66" spans="1:14" ht="12.75">
       <c r="A66" t="s">
@@ -8599,9 +8401,6 @@
       <c r="M66">
         <v>0.99952095808383201</v>
       </c>
-      <c r="N66" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="67" spans="1:14" ht="12.75">
       <c r="A67" t="s">
@@ -8643,9 +8442,6 @@
       <c r="M67">
         <v>3.0897837837837798</v>
       </c>
-      <c r="N67" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="68" spans="1:14" ht="12.75">
       <c r="A68" t="s">
@@ -8687,9 +8483,6 @@
       <c r="M68">
         <v>0.90000000000000002</v>
       </c>
-      <c r="N68" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="69" spans="1:14" ht="12.75">
       <c r="A69" t="s">
@@ -8731,9 +8524,6 @@
       <c r="M69">
         <v>0.82728758169934602</v>
       </c>
-      <c r="N69" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="70" spans="1:14" ht="12.75">
       <c r="A70" t="s">
@@ -8775,9 +8565,6 @@
       <c r="M70">
         <v>0.65865731206453004</v>
       </c>
-      <c r="N70" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="71" spans="1:14" ht="12.75">
       <c r="A71" t="s">
@@ -8819,9 +8606,6 @@
       <c r="M71">
         <v>0.82280373831775699</v>
       </c>
-      <c r="N71" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="72" spans="1:14" ht="12.75">
       <c r="A72" t="s">
@@ -8863,9 +8647,6 @@
       <c r="M72">
         <v>0.82661774762699303</v>
       </c>
-      <c r="N72" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="73" spans="1:14" ht="12.75">
       <c r="A73" t="s">
@@ -8907,9 +8688,6 @@
       <c r="M73">
         <v>0.54578947368421105</v>
       </c>
-      <c r="N73" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="74" spans="1:14" ht="12.75">
       <c r="A74" t="s">
@@ -8951,9 +8729,6 @@
       <c r="M74">
         <v>0.61474226804123699</v>
       </c>
-      <c r="N74" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="75" spans="1:14" ht="12.75">
       <c r="A75" t="s">
@@ -8995,9 +8770,6 @@
       <c r="M75">
         <v>1</v>
       </c>
-      <c r="N75" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="76" spans="1:14" ht="12.75">
       <c r="A76" t="s">
@@ -9038,9 +8810,6 @@
       </c>
       <c r="M76">
         <v>0.72928609692169399</v>
-      </c>
-      <c r="N76" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -9094,9 +8863,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -9137,9 +8903,6 @@
       </c>
       <c r="M2">
         <v>0.010896637608966401</v>
-      </c>
-      <c r="N2" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -9193,9 +8956,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -9205,7 +8965,7 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D2" t="s">
         <v>131</v>
@@ -9236,9 +8996,6 @@
       </c>
       <c r="M2">
         <v>0.12716586319930701</v>
-      </c>
-      <c r="N2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="12.75">
@@ -9281,9 +9038,6 @@
       <c r="M3">
         <v>0.24175608869574</v>
       </c>
-      <c r="N3" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="4" spans="1:14" ht="12.75">
       <c r="A4" t="s">
@@ -9293,7 +9047,7 @@
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D4" t="s">
         <v>131</v>
@@ -9324,9 +9078,6 @@
       </c>
       <c r="M4">
         <v>0.29872122806778101</v>
-      </c>
-      <c r="N4" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -9380,9 +9131,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -9423,9 +9171,6 @@
       </c>
       <c r="M2">
         <v>0.0118630136986301</v>
-      </c>
-      <c r="N2" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -9482,9 +9227,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -9494,7 +9236,7 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
         <v>131</v>
@@ -9525,9 +9267,6 @@
       </c>
       <c r="M2">
         <v>0.21098594733224099</v>
-      </c>
-      <c r="N2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="12.75">
@@ -9570,9 +9309,6 @@
       <c r="M3">
         <v>0.29847129365993402</v>
       </c>
-      <c r="N3" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="4" spans="1:14" ht="12.75">
       <c r="A4" t="s">
@@ -9582,7 +9318,7 @@
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D4" t="s">
         <v>131</v>
@@ -9613,9 +9349,6 @@
       </c>
       <c r="M4">
         <v>0.49065561985780998</v>
-      </c>
-      <c r="N4" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -9669,9 +9402,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -9712,9 +9442,6 @@
       </c>
       <c r="M2">
         <v>0.0067195931921959296</v>
-      </c>
-      <c r="N2" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -9768,9 +9495,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -9780,7 +9504,7 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D2" t="s">
         <v>131</v>
@@ -9811,9 +9535,6 @@
       </c>
       <c r="M2">
         <v>0.0121865123037202</v>
-      </c>
-      <c r="N2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="12.75">
@@ -9856,9 +9577,6 @@
       <c r="M3">
         <v>0.0104455975746106</v>
       </c>
-      <c r="N3" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="4" spans="1:14" ht="12.75">
       <c r="A4" t="s">
@@ -9868,7 +9586,7 @@
         <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D4" t="s">
         <v>131</v>
@@ -9899,9 +9617,6 @@
       </c>
       <c r="M4">
         <v>0.010445583301088201</v>
-      </c>
-      <c r="N4" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -9955,9 +9670,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -9998,9 +9710,6 @@
       </c>
       <c r="M2">
         <v>0.117199391171994</v>
-      </c>
-      <c r="N2" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -10054,9 +9763,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -10097,9 +9803,6 @@
       </c>
       <c r="M2">
         <v>0.93569571451266098</v>
-      </c>
-      <c r="N2" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -17352,9 +17055,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -17396,9 +17096,6 @@
       <c r="M2">
         <v>0.12</v>
       </c>
-      <c r="N2" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="3" spans="1:14" ht="12.75">
       <c r="A3" t="s">
@@ -17440,9 +17137,6 @@
       <c r="M3">
         <v>0.12</v>
       </c>
-      <c r="N3" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="4" spans="1:14" ht="12.75">
       <c r="A4" t="s">
@@ -17484,9 +17178,6 @@
       <c r="M4">
         <v>0.053377456313566302</v>
       </c>
-      <c r="N4" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="5" spans="1:14" ht="12.75">
       <c r="A5" t="s">
@@ -17528,9 +17219,6 @@
       <c r="M5">
         <v>0.49058779213070902</v>
       </c>
-      <c r="N5" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="6" spans="1:14" ht="12.75">
       <c r="A6" t="s">
@@ -17572,9 +17260,6 @@
       <c r="M6">
         <v>0.12</v>
       </c>
-      <c r="N6" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="7" spans="1:14" ht="12.75">
       <c r="A7" t="s">
@@ -17616,9 +17301,6 @@
       <c r="M7">
         <v>0.060645497051149098</v>
       </c>
-      <c r="N7" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="8" spans="1:14" ht="12.75">
       <c r="A8" t="s">
@@ -17660,9 +17342,6 @@
       <c r="M8">
         <v>0.12</v>
       </c>
-      <c r="N8" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="9" spans="1:14" ht="12.75">
       <c r="A9" t="s">
@@ -17704,9 +17383,6 @@
       <c r="M9">
         <v>0.12</v>
       </c>
-      <c r="N9" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="10" spans="1:14" ht="12.75">
       <c r="A10" t="s">
@@ -17748,9 +17424,6 @@
       <c r="M10">
         <v>0.12</v>
       </c>
-      <c r="N10" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="11" spans="1:14" ht="12.75">
       <c r="A11" t="s">
@@ -17792,9 +17465,6 @@
       <c r="M11">
         <v>0.12</v>
       </c>
-      <c r="N11" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="12" spans="1:14" ht="12.75">
       <c r="A12" t="s">
@@ -17836,9 +17506,6 @@
       <c r="M12">
         <v>0.12</v>
       </c>
-      <c r="N12" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="13" spans="1:14" ht="12.75">
       <c r="A13" t="s">
@@ -17880,9 +17547,6 @@
       <c r="M13">
         <v>0.13976565562716001</v>
       </c>
-      <c r="N13" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="14" spans="1:14" ht="12.75">
       <c r="A14" t="s">
@@ -17924,9 +17588,6 @@
       <c r="M14">
         <v>0.12</v>
       </c>
-      <c r="N14" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="15" spans="1:14" ht="12.75">
       <c r="A15" t="s">
@@ -17968,9 +17629,6 @@
       <c r="M15">
         <v>0.12</v>
       </c>
-      <c r="N15" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="16" spans="1:14" ht="12.75">
       <c r="A16" t="s">
@@ -18012,9 +17670,6 @@
       <c r="M16">
         <v>0.10081773520747001</v>
       </c>
-      <c r="N16" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="17" spans="1:14" ht="12.75">
       <c r="A17" t="s">
@@ -18056,9 +17711,6 @@
       <c r="M17">
         <v>0.062077936363827101</v>
       </c>
-      <c r="N17" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="18" spans="1:14" ht="12.75">
       <c r="A18" t="s">
@@ -18100,9 +17752,6 @@
       <c r="M18">
         <v>0.66299984214582297</v>
       </c>
-      <c r="N18" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="19" spans="1:14" ht="12.75">
       <c r="A19" t="s">
@@ -18144,9 +17793,6 @@
       <c r="M19">
         <v>0.12</v>
       </c>
-      <c r="N19" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="20" spans="1:14" ht="12.75">
       <c r="A20" t="s">
@@ -18188,9 +17834,6 @@
       <c r="M20">
         <v>0.049806776874505597</v>
       </c>
-      <c r="N20" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="21" spans="1:14" ht="12.75">
       <c r="A21" t="s">
@@ -18232,9 +17875,6 @@
       <c r="M21">
         <v>0.12</v>
       </c>
-      <c r="N21" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="22" spans="1:14" ht="12.75">
       <c r="A22" t="s">
@@ -18276,9 +17916,6 @@
       <c r="M22">
         <v>0.069903120588175702</v>
       </c>
-      <c r="N22" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="23" spans="1:14" ht="12.75">
       <c r="A23" t="s">
@@ -18320,9 +17957,6 @@
       <c r="M23">
         <v>0.12</v>
       </c>
-      <c r="N23" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="24" spans="1:14" ht="12.75">
       <c r="A24" t="s">
@@ -18364,9 +17998,6 @@
       <c r="M24">
         <v>0.12</v>
       </c>
-      <c r="N24" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="25" spans="1:14" ht="12.75">
       <c r="A25" t="s">
@@ -18408,9 +18039,6 @@
       <c r="M25">
         <v>0.057147241043066198</v>
       </c>
-      <c r="N25" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="26" spans="1:14" ht="12.75">
       <c r="A26" t="s">
@@ -18452,9 +18080,6 @@
       <c r="M26">
         <v>0.21413130493478699</v>
       </c>
-      <c r="N26" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="27" spans="1:14" ht="12.75">
       <c r="A27" t="s">
@@ -18496,9 +18121,6 @@
       <c r="M27">
         <v>0.12</v>
       </c>
-      <c r="N27" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="28" spans="1:14" ht="12.75">
       <c r="A28" t="s">
@@ -18540,9 +18162,6 @@
       <c r="M28">
         <v>0.12</v>
       </c>
-      <c r="N28" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="29" spans="1:14" ht="12.75">
       <c r="A29" t="s">
@@ -18584,9 +18203,6 @@
       <c r="M29">
         <v>0.12</v>
       </c>
-      <c r="N29" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="30" spans="1:14" ht="12.75">
       <c r="A30" t="s">
@@ -18628,9 +18244,6 @@
       <c r="M30">
         <v>0.12</v>
       </c>
-      <c r="N30" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="31" spans="1:14" ht="12.75">
       <c r="A31" t="s">
@@ -18672,9 +18285,6 @@
       <c r="M31">
         <v>0.12</v>
       </c>
-      <c r="N31" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="32" spans="1:14" ht="12.75">
       <c r="A32" t="s">
@@ -18716,9 +18326,6 @@
       <c r="M32">
         <v>0.12</v>
       </c>
-      <c r="N32" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="33" spans="1:14" ht="12.75">
       <c r="A33" t="s">
@@ -18760,9 +18367,6 @@
       <c r="M33">
         <v>0.042554933846820402</v>
       </c>
-      <c r="N33" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="34" spans="1:14" ht="12.75">
       <c r="A34" t="s">
@@ -18804,9 +18408,6 @@
       <c r="M34">
         <v>0.12</v>
       </c>
-      <c r="N34" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="35" spans="1:14" ht="12.75">
       <c r="A35" t="s">
@@ -18848,9 +18449,6 @@
       <c r="M35">
         <v>0.0537114750791833</v>
       </c>
-      <c r="N35" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="36" spans="1:14" ht="12.75">
       <c r="A36" t="s">
@@ -18892,9 +18490,6 @@
       <c r="M36">
         <v>0.12</v>
       </c>
-      <c r="N36" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="37" spans="1:14" ht="12.75">
       <c r="A37" t="s">
@@ -18936,9 +18531,6 @@
       <c r="M37">
         <v>0.12</v>
       </c>
-      <c r="N37" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="38" spans="1:14" ht="12.75">
       <c r="A38" t="s">
@@ -18980,9 +18572,6 @@
       <c r="M38">
         <v>0.043752307505030202</v>
       </c>
-      <c r="N38" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="39" spans="1:14" ht="12.75">
       <c r="A39" t="s">
@@ -19024,9 +18613,6 @@
       <c r="M39">
         <v>0.14341496381045399</v>
       </c>
-      <c r="N39" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="40" spans="1:14" ht="12.75">
       <c r="A40" t="s">
@@ -19067,9 +18653,6 @@
       </c>
       <c r="M40">
         <v>0.12</v>
-      </c>
-      <c r="N40" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -19126,9 +18709,6 @@
       <c r="M1" t="s">
         <v>9</v>
       </c>
-      <c r="N1" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="2" spans="1:14" ht="12.75">
       <c r="A2" t="s">
@@ -19170,9 +18750,6 @@
       <c r="M2">
         <v>0.12</v>
       </c>
-      <c r="N2" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="3" spans="1:14" ht="12.75">
       <c r="A3" t="s">
@@ -19214,9 +18791,6 @@
       <c r="M3">
         <v>0.12</v>
       </c>
-      <c r="N3" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="4" spans="1:14" ht="12.75">
       <c r="A4" t="s">
@@ -19258,9 +18832,6 @@
       <c r="M4">
         <v>0.013931119040235</v>
       </c>
-      <c r="N4" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="5" spans="1:14" ht="12.75">
       <c r="A5" t="s">
@@ -19302,9 +18873,6 @@
       <c r="M5">
         <v>0.18130269923092601</v>
       </c>
-      <c r="N5" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="6" spans="1:14" ht="12.75">
       <c r="A6" t="s">
@@ -19346,9 +18914,6 @@
       <c r="M6">
         <v>0.12</v>
       </c>
-      <c r="N6" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="7" spans="1:14" ht="12.75">
       <c r="A7" t="s">
@@ -19390,9 +18955,6 @@
       <c r="M7">
         <v>0.025618485673577399</v>
       </c>
-      <c r="N7" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="8" spans="1:14" ht="12.75">
       <c r="A8" t="s">
@@ -19434,9 +18996,6 @@
       <c r="M8">
         <v>0.12</v>
       </c>
-      <c r="N8" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="9" spans="1:14" ht="12.75">
       <c r="A9" t="s">
@@ -19478,9 +19037,6 @@
       <c r="M9">
         <v>0.066604254563694898</v>
       </c>
-      <c r="N9" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="10" spans="1:14" ht="12.75">
       <c r="A10" t="s">
@@ -19522,9 +19078,6 @@
       <c r="M10">
         <v>0.12</v>
       </c>
-      <c r="N10" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="11" spans="1:14" ht="12.75">
       <c r="A11" t="s">
@@ -19566,9 +19119,6 @@
       <c r="M11">
         <v>0.161743747694956</v>
       </c>
-      <c r="N11" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="12" spans="1:14" ht="12.75">
       <c r="A12" t="s">
@@ -19610,9 +19160,6 @@
       <c r="M12">
         <v>0.12</v>
       </c>
-      <c r="N12" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="13" spans="1:14" ht="12.75">
       <c r="A13" t="s">
@@ -19654,9 +19201,6 @@
       <c r="M13">
         <v>0.12</v>
       </c>
-      <c r="N13" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="14" spans="1:14" ht="12.75">
       <c r="A14" t="s">
@@ -19698,9 +19242,6 @@
       <c r="M14">
         <v>0.12</v>
       </c>
-      <c r="N14" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="15" spans="1:14" ht="12.75">
       <c r="A15" t="s">
@@ -19742,9 +19283,6 @@
       <c r="M15">
         <v>0.30984484845142601</v>
       </c>
-      <c r="N15" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="16" spans="1:14" ht="12.75">
       <c r="A16" t="s">
@@ -19786,9 +19324,6 @@
       <c r="M16">
         <v>0.035156391297092499</v>
       </c>
-      <c r="N16" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="17" spans="1:14" ht="12.75">
       <c r="A17" t="s">
@@ -19830,9 +19365,6 @@
       <c r="M17">
         <v>0.11404303534564</v>
       </c>
-      <c r="N17" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="18" spans="1:14" ht="12.75">
       <c r="A18" t="s">
@@ -19874,9 +19406,6 @@
       <c r="M18">
         <v>0.12</v>
       </c>
-      <c r="N18" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="19" spans="1:14" ht="12.75">
       <c r="A19" t="s">
@@ -19918,9 +19447,6 @@
       <c r="M19">
         <v>0.035964557684536103</v>
       </c>
-      <c r="N19" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="20" spans="1:14" ht="12.75">
       <c r="A20" t="s">
@@ -19962,9 +19488,6 @@
       <c r="M20">
         <v>0.12</v>
       </c>
-      <c r="N20" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="21" spans="1:14" ht="12.75">
       <c r="A21" t="s">
@@ -20006,9 +19529,6 @@
       <c r="M21">
         <v>0.047079298490866298</v>
       </c>
-      <c r="N21" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="22" spans="1:14" ht="12.75">
       <c r="A22" t="s">
@@ -20050,9 +19570,6 @@
       <c r="M22">
         <v>0.048109166237074001</v>
       </c>
-      <c r="N22" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="23" spans="1:14" ht="12.75">
       <c r="A23" t="s">
@@ -20094,9 +19611,6 @@
       <c r="M23">
         <v>0.0727790788417393</v>
       </c>
-      <c r="N23" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="24" spans="1:14" ht="12.75">
       <c r="A24" t="s">
@@ -20138,9 +19652,6 @@
       <c r="M24">
         <v>0.072438724233275797</v>
       </c>
-      <c r="N24" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="25" spans="1:14" ht="12.75">
       <c r="A25" t="s">
@@ -20182,9 +19693,6 @@
       <c r="M25">
         <v>0.12</v>
       </c>
-      <c r="N25" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="26" spans="1:14" ht="12.75">
       <c r="A26" t="s">
@@ -20226,9 +19734,6 @@
       <c r="M26">
         <v>0.0697946718860816</v>
       </c>
-      <c r="N26" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="27" spans="1:14" ht="12.75">
       <c r="A27" t="s">
@@ -20270,9 +19775,6 @@
       <c r="M27">
         <v>0.46414376338591401</v>
       </c>
-      <c r="N27" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="28" spans="1:14" ht="12.75">
       <c r="A28" t="s">
@@ -20314,9 +19816,6 @@
       <c r="M28">
         <v>0.043843217634644903</v>
       </c>
-      <c r="N28" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="29" spans="1:14" ht="12.75">
       <c r="A29" t="s">
@@ -20358,9 +19857,6 @@
       <c r="M29">
         <v>0.138319067250922</v>
       </c>
-      <c r="N29" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="30" spans="1:14" ht="12.75">
       <c r="A30" t="s">
@@ -20402,9 +19898,6 @@
       <c r="M30">
         <v>0.0697946718860816</v>
       </c>
-      <c r="N30" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="31" spans="1:14" ht="12.75">
       <c r="A31" t="s">
@@ -20446,9 +19939,6 @@
       <c r="M31">
         <v>0.0396720040920054</v>
       </c>
-      <c r="N31" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="32" spans="1:14" ht="12.75">
       <c r="A32" t="s">
@@ -20490,9 +19980,6 @@
       <c r="M32">
         <v>0.12</v>
       </c>
-      <c r="N32" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="33" spans="1:14" ht="12.75">
       <c r="A33" t="s">
@@ -20534,9 +20021,6 @@
       <c r="M33">
         <v>0.0537535468762151</v>
       </c>
-      <c r="N33" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="34" spans="1:14" ht="12.75">
       <c r="A34" t="s">
@@ -20578,9 +20062,6 @@
       <c r="M34">
         <v>0.0697946718860816</v>
       </c>
-      <c r="N34" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="35" spans="1:14" ht="12.75">
       <c r="A35" t="s">
@@ -20622,9 +20103,6 @@
       <c r="M35">
         <v>0.101539467044872</v>
       </c>
-      <c r="N35" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="36" spans="1:14" ht="12.75">
       <c r="A36" t="s">
@@ -20666,9 +20144,6 @@
       <c r="M36">
         <v>0.13495608652757701</v>
       </c>
-      <c r="N36" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="37" spans="1:14" ht="12.75">
       <c r="A37" t="s">
@@ -20709,9 +20184,6 @@
       </c>
       <c r="M37">
         <v>0.094687203541950801</v>
-      </c>
-      <c r="N37" t="s">
-        <v>131</v>
       </c>
     </row>
   </sheetData>
